--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -631,7 +631,7 @@
     <t>Identifikator for pasienten.</t>
   </si>
   <si>
-    <t>Identifikator for pasienten. Skal være fødselsnummer (FNR) eller D-nummer (DNR).</t>
+    <t>Identifikator for pasienten. Bør være fødselsnummer (FNR) eller D-nummer (DNR) når tilgjengelig.</t>
   </si>
   <si>
     <t>Patients are almost always assigned specific numerical identifiers.</t>
@@ -1384,10 +1384,6 @@
   </si>
   <si>
     <t>Address.use</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-address-use-constraint:Kun home, temp eller old er tillatt for address.use {address.use.empty() or address.use in ('home' | 'temp' | 'old')}</t>
   </si>
   <si>
     <t>Patient.address.type</t>
@@ -11120,15 +11116,15 @@
         <v>94</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>439</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11154,13 +11150,13 @@
         <v>103</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11171,10 +11167,10 @@
         <v>76</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>76</v>
@@ -11190,25 +11186,25 @@
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11225,10 +11221,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11254,16 +11250,16 @@
         <v>143</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>76</v>
@@ -11276,43 +11272,43 @@
         <v>76</v>
       </c>
       <c r="T88" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF88" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>
@@ -11329,10 +11325,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11358,10 +11354,10 @@
         <v>143</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>335</v>
@@ -11378,43 +11374,43 @@
         <v>76</v>
       </c>
       <c r="T89" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
@@ -11431,14 +11427,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11460,10 +11456,10 @@
         <v>143</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>335</v>
@@ -11480,43 +11476,43 @@
         <v>76</v>
       </c>
       <c r="T90" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF90" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -11533,14 +11529,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11562,13 +11558,13 @@
         <v>143</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -11582,43 +11578,43 @@
         <v>76</v>
       </c>
       <c r="T91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
@@ -11635,10 +11631,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11735,10 +11731,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11837,13 +11833,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>76</v>
@@ -11865,13 +11861,13 @@
         <v>76</v>
       </c>
       <c r="K94" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L94" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L94" t="s" s="2">
+      <c r="M94" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11939,10 +11935,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11968,10 +11964,10 @@
         <v>143</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11995,34 +11991,34 @@
         <v>76</v>
       </c>
       <c r="W95" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12039,14 +12035,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12068,10 +12064,10 @@
         <v>143</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>335</v>
@@ -12124,7 +12120,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12141,14 +12137,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12170,10 +12166,10 @@
         <v>143</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M97" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>335</v>
@@ -12190,43 +12186,43 @@
         <v>76</v>
       </c>
       <c r="T97" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12243,10 +12239,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12272,13 +12268,13 @@
         <v>143</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12328,7 +12324,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -12345,10 +12341,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12374,16 +12370,16 @@
         <v>181</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>248</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -12396,43 +12392,43 @@
         <v>76</v>
       </c>
       <c r="T99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -12449,10 +12445,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12478,16 +12474,16 @@
         <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>76</v>
@@ -12515,11 +12511,11 @@
         <v>223</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="Z100" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="AA100" t="s" s="2">
         <v>76</v>
       </c>
@@ -12536,7 +12532,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -12553,10 +12549,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12579,19 +12575,19 @@
         <v>76</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>76</v>
@@ -12640,7 +12636,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12657,10 +12653,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12683,19 +12679,19 @@
         <v>76</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="N102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -12744,7 +12740,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -12756,15 +12752,15 @@
         <v>94</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12787,19 +12783,19 @@
         <v>76</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -12848,7 +12844,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12860,15 +12856,15 @@
         <v>94</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12965,10 +12961,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13067,14 +13063,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13096,10 +13092,10 @@
         <v>127</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>130</v>
@@ -13154,7 +13150,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -13171,10 +13167,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13200,16 +13196,16 @@
         <v>169</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>76</v>
@@ -13237,11 +13233,11 @@
         <v>223</v>
       </c>
       <c r="Y107" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z107" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z107" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA107" t="s" s="2">
         <v>76</v>
       </c>
@@ -13258,7 +13254,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
@@ -13275,10 +13271,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13313,7 +13309,7 @@
         <v>378</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -13362,7 +13358,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -13379,10 +13375,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13408,13 +13404,13 @@
         <v>381</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>385</v>
@@ -13466,7 +13462,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
@@ -13483,10 +13479,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13512,16 +13508,16 @@
         <v>407</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>410</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>76</v>
@@ -13570,7 +13566,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
@@ -13587,10 +13583,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13616,16 +13612,16 @@
         <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="N111" t="s" s="2">
         <v>335</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13674,7 +13670,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -13691,10 +13687,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13720,16 +13716,16 @@
         <v>253</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="M112" t="s" s="2">
+      <c r="N112" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="N112" t="s" s="2">
+      <c r="O112" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
@@ -13778,7 +13774,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13787,7 +13783,7 @@
         <v>82</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>258</v>
@@ -13795,10 +13791,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13824,10 +13820,10 @@
         <v>181</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>248</v>
@@ -13880,7 +13876,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13897,10 +13893,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13923,19 +13919,19 @@
         <v>76</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -13984,7 +13980,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -14001,10 +13997,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14101,10 +14097,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14203,14 +14199,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -14232,10 +14228,10 @@
         <v>127</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>130</v>
@@ -14290,7 +14286,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14307,10 +14303,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14336,16 +14332,16 @@
         <v>169</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="N118" t="s" s="2">
+      <c r="O118" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>76</v>
@@ -14394,7 +14390,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -14411,10 +14407,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14440,16 +14436,16 @@
         <v>346</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>585</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -14498,7 +14494,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -14515,14 +14511,14 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -14541,16 +14537,16 @@
         <v>76</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="L120" t="s" s="2">
+      <c r="M120" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -14600,7 +14596,7 @@
         <v>76</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
@@ -14617,10 +14613,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14643,19 +14639,19 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="N121" t="s" s="2">
+      <c r="O121" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>76</v>
@@ -14704,7 +14700,7 @@
         <v>76</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
@@ -14721,10 +14717,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14747,19 +14743,19 @@
         <v>83</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="N122" t="s" s="2">
+      <c r="O122" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>76</v>
@@ -14808,7 +14804,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
@@ -14825,10 +14821,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14925,10 +14921,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15027,14 +15023,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -15056,10 +15052,10 @@
         <v>127</v>
       </c>
       <c r="L125" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M125" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>130</v>
@@ -15114,7 +15110,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15131,10 +15127,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15157,16 +15153,16 @@
         <v>83</v>
       </c>
       <c r="K126" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L126" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="L126" t="s" s="2">
+      <c r="M126" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -15216,7 +15212,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -15233,10 +15229,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15262,10 +15258,10 @@
         <v>103</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="M127" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>335</v>
@@ -15297,11 +15293,11 @@
         <v>213</v>
       </c>
       <c r="Y127" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="Z127" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="Z127" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="AA127" t="s" s="2">
         <v>76</v>
       </c>
@@ -15318,7 +15314,7 @@
         <v>76</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-patient.xlsx
+++ b/StructureDefinition-lmdi-patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
